--- a/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
+++ b/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Входные данные" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Расчёт" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Итог для документа" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Пример заполнения" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Входные данные" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Расчёт" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итог для документа" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Пример заполнения" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="G46" s="15">
-        <f>ROUND('Входные данные'!$B$4+$G$45,2)</f>
+        <f>ROUND('Входные данные'!$B$4-SUM('Входные данные'!$B$35:$B$44)+$G$45,2)</f>
         <v/>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Сумма долга, руб.</t>
+          <t>Сумма долга по актам, руб.</t>
         </is>
       </c>
       <c r="B4" s="17">
@@ -2066,54 +2066,76 @@
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Период начисления с</t>
-        </is>
-      </c>
-      <c r="B5" s="18">
-        <f>'Входные данные'!$B$5</f>
+          <t>Учтено частичных оплат, руб.</t>
+        </is>
+      </c>
+      <c r="B5" s="17">
+        <f>ROUND(SUM('Входные данные'!$B$35:$B$44),2)</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Период начисления по</t>
-        </is>
-      </c>
-      <c r="B6" s="18">
-        <f>'Входные данные'!$B$6</f>
+          <t>Основной долг к взысканию, руб.</t>
+        </is>
+      </c>
+      <c r="B6" s="17">
+        <f>ROUND('Входные данные'!$B$4-SUM('Входные данные'!$B$35:$B$44),2)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>Всего дней просрочки</t>
-        </is>
-      </c>
-      <c r="B7" s="19">
-        <f>IF(OR('Входные данные'!$B$5="",'Входные данные'!$B$6=""),"",'Входные данные'!$B$6-'Входные данные'!$B$5+1)</f>
+          <t>Период начисления с</t>
+        </is>
+      </c>
+      <c r="B7" s="18">
+        <f>'Входные данные'!$B$5</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>Проценты по ст. 395 ГК РФ, руб.</t>
-        </is>
-      </c>
-      <c r="B8" s="17">
-        <f>'Расчёт'!$G$45</f>
+          <t>Период начисления по</t>
+        </is>
+      </c>
+      <c r="B8" s="18">
+        <f>'Входные данные'!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
+          <t>Всего дней просрочки</t>
+        </is>
+      </c>
+      <c r="B9" s="19">
+        <f>IF(OR('Входные данные'!$B$5="",'Входные данные'!$B$6=""),"",'Входные данные'!$B$6-'Входные данные'!$B$5+1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Проценты по ст. 395 ГК РФ, руб.</t>
+        </is>
+      </c>
+      <c r="B10" s="17">
+        <f>'Расчёт'!$G$45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
           <t>Итого к взысканию, руб.</t>
         </is>
       </c>
-      <c r="B9" s="17">
+      <c r="B11" s="17">
         <f>'Расчёт'!$G$46</f>
         <v/>
       </c>

--- a/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
+++ b/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
@@ -2055,7 +2055,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Сумма долга по актам, руб.</t>
+          <t>Сумма долга на начало расчёта, руб.</t>
         </is>
       </c>
       <c r="B4" s="17">

--- a/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
+++ b/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
@@ -2031,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2182,12 +2182,20 @@
         </is>
       </c>
     </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>— Юридическую консультацию и вычитку юристом. Порядок расчёта сверен с текстом действующих норм 15.08.2026: нормативная сверка сопоставляет формулировки и порядок со статьями закона и правовой позиции по вашему спору не оценивает.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
+++ b/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
@@ -764,7 +764,7 @@
     <row r="47" ht="64" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Частичная оплата по ст. 319 ГК РФ по общему правилу гасит сначала издержки и проценты, затем основной долг — если платёжное поручение не говорит иного. Эта таблица уменьшает базу долга на сумму оплаты с её даты, то есть считает по простому варианту. Как разносить частичные оплаты в спорной ситуации — вопрос к юристу: если очерёдность имеет значение для вашего спора, расчёт надо корректировать.</t>
+          <t>Частичная оплата по ст. 319 ГК РФ гасит сначала издержки, затем проценты и только потом основной долг. Отступить от этой очерёдности можно соглашением сторон; одностороннее указание в платёжном поручении соглашением не является и очерёдность не меняет. Порядок такой: есть допустимое соглашение — считайте по нему; соглашения нет — по ст. 319 ГК РФ. Если однородных обязательств несколько, выбор погашаемого — отдельный вопрос, и его решают не здесь. Эта таблица уменьшает базу долга на сумму оплаты с её даты, то есть считает по простому варианту: если очерёдность имеет значение для вашего спора, расчёт надо корректировать с юристом.</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
     <row r="48" ht="46" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Число дней в году берётся фактическое — 365 или 366. Такой подход соответствует практике применения ст. 395 ГК РФ (постановление Пленума Верховного Суда РФ от 24.03.2016 № 7 «О применении судами некоторых положений Гражданского кодекса Российской Федерации об ответственности за нарушение обязательств», действует в редакции от 22.06.2021).</t>
+          <t>Число дней в году берётся фактическое — 365 или 366. Формула считает по фактическому числу дней; норму, которая устанавливала бы иной знаменатель, этот расчёт не применяет. Если для вашего спора знаменатель принципиален, сверьте его с юристом по действующей практике на дату расчёта.</t>
         </is>
       </c>
     </row>

--- a/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
+++ b/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
@@ -572,7 +572,7 @@
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>День, следующий за последним днём срока оплаты по договору.</t>
+          <t>День, следующий за последним днём срока оплаты по договору. Если этот последний день пришёлся на нерабочий, срок оплаты по ст. 193 ГК РФ истекает в ближайший следующий рабочий день, и просрочка начинается со дня после него.</t>
         </is>
       </c>
     </row>

--- a/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
+++ b/products-storage/04-polnyy-komplekt-pto/01-30-bazovye-pakety/01-zakrytie-rabot/14-raschet-procentov-395-gk.xlsx
@@ -2185,7 +2185,7 @@
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>— Юридическую консультацию и вычитку юристом. Порядок расчёта сверен с текстом действующих норм 15.08.2026: нормативная сверка сопоставляет формулировки и порядок со статьями закона и правовой позиции по вашему спору не оценивает.</t>
+          <t>— Юридическую консультацию и вычитку юристом. Порядок расчёта сверен с текстом действующих норм 16.08.2026: нормативная сверка сопоставляет формулировки и порядок со статьями закона и правовой позиции по вашему спору не оценивает.</t>
         </is>
       </c>
     </row>
